--- a/57.xlsx
+++ b/57.xlsx
@@ -511,7 +511,7 @@
         <v>0.304724782705307</v>
       </c>
       <c r="K2" t="n">
-        <v>8.92160000057629e-06</v>
+        <v>2.706360000047425e-05</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>0.3108069598674774</v>
       </c>
       <c r="K3" t="n">
-        <v>5.276599999888276e-06</v>
+        <v>5.6760999996186e-06</v>
       </c>
     </row>
     <row r="4">
@@ -593,7 +593,7 @@
         <v>0.3064090311527252</v>
       </c>
       <c r="K4" t="n">
-        <v>5.441999999675318e-06</v>
+        <v>5.827299999509705e-06</v>
       </c>
     </row>
     <row r="5">
@@ -634,7 +634,7 @@
         <v>0.3084602057933807</v>
       </c>
       <c r="K5" t="n">
-        <v>5.736699999943085e-06</v>
+        <v>5.827799999678973e-06</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>0.3026606142520905</v>
       </c>
       <c r="K6" t="n">
-        <v>5.561500000112573e-06</v>
+        <v>6.675700000414509e-06</v>
       </c>
     </row>
     <row r="7">
@@ -716,7 +716,7 @@
         <v>0.2876628041267395</v>
       </c>
       <c r="K7" t="n">
-        <v>5.636199999571545e-06</v>
+        <v>5.741200000557001e-06</v>
       </c>
     </row>
     <row r="8">
@@ -757,7 +757,7 @@
         <v>0.281400203704834</v>
       </c>
       <c r="K8" t="n">
-        <v>5.251100000350561e-06</v>
+        <v>5.83569999980682e-06</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.2835347056388855</v>
       </c>
       <c r="K9" t="n">
-        <v>8.142099999531638e-06</v>
+        <v>6.47690000005241e-06</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.2849827110767365</v>
       </c>
       <c r="K10" t="n">
-        <v>6.511800000225776e-06</v>
+        <v>5.565600000409177e-06</v>
       </c>
     </row>
     <row r="11">
@@ -880,7 +880,7 @@
         <v>0.2848705351352692</v>
       </c>
       <c r="K11" t="n">
-        <v>5.69550000000163e-06</v>
+        <v>6.488299999546143e-06</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         <v>0.3029690682888031</v>
       </c>
       <c r="K12" t="n">
-        <v>5.606300000181363e-06</v>
+        <v>6.079000000681844e-06</v>
       </c>
     </row>
     <row r="13">
@@ -962,7 +962,7 @@
         <v>0.3073286116123199</v>
       </c>
       <c r="K13" t="n">
-        <v>5.14019999991433e-06</v>
+        <v>6.391900000380701e-06</v>
       </c>
     </row>
     <row r="14">
@@ -1003,7 +1003,7 @@
         <v>0.305938184261322</v>
       </c>
       <c r="K14" t="n">
-        <v>5.721300000004703e-06</v>
+        <v>5.572699999902397e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1044,7 +1044,7 @@
         <v>0.3058680295944214</v>
       </c>
       <c r="K15" t="n">
-        <v>5.885399999897345e-06</v>
+        <v>5.407399999967311e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1085,7 +1085,7 @@
         <v>0.3027482926845551</v>
       </c>
       <c r="K16" t="n">
-        <v>5.530399999770452e-06</v>
+        <v>5.210200000874465e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1126,7 +1126,7 @@
         <v>0.3149725496768951</v>
       </c>
       <c r="K17" t="n">
-        <v>9.866100000181177e-06</v>
+        <v>9.88590000088152e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1167,7 +1167,7 @@
         <v>0.3141289055347443</v>
       </c>
       <c r="K18" t="n">
-        <v>7.995199999641045e-06</v>
+        <v>8.367300000827526e-06</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>0.3117594718933105</v>
       </c>
       <c r="K19" t="n">
-        <v>8.241499999712687e-06</v>
+        <v>7.962699999552569e-06</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.3145458400249481</v>
       </c>
       <c r="K20" t="n">
-        <v>7.749999999759894e-06</v>
+        <v>7.758699999612873e-06</v>
       </c>
     </row>
     <row r="21">
@@ -1290,7 +1290,7 @@
         <v>0.3127709329128265</v>
       </c>
       <c r="K21" t="n">
-        <v>7.365100000242819e-06</v>
+        <v>8.41010000112874e-06</v>
       </c>
     </row>
     <row r="22">
@@ -1331,7 +1331,7 @@
         <v>0.2798687517642975</v>
       </c>
       <c r="K22" t="n">
-        <v>7.325500000661122e-06</v>
+        <v>7.588599999508006e-06</v>
       </c>
     </row>
     <row r="23">
@@ -1372,7 +1372,7 @@
         <v>0.294763058423996</v>
       </c>
       <c r="K23" t="n">
-        <v>7.834699999875738e-06</v>
+        <v>7.538300000305753e-06</v>
       </c>
     </row>
     <row r="24">
@@ -1413,7 +1413,7 @@
         <v>0.302911102771759</v>
       </c>
       <c r="K24" t="n">
-        <v>7.740000000012514e-06</v>
+        <v>7.897899999079527e-06</v>
       </c>
     </row>
     <row r="25">
@@ -1454,7 +1454,7 @@
         <v>0.2694041430950165</v>
       </c>
       <c r="K25" t="n">
-        <v>8.065099999839731e-06</v>
+        <v>7.763600000544101e-06</v>
       </c>
     </row>
     <row r="26">
@@ -1495,7 +1495,7 @@
         <v>0.2688374519348145</v>
       </c>
       <c r="K26" t="n">
-        <v>7.847799999581184e-06</v>
+        <v>8.927400000175112e-06</v>
       </c>
     </row>
   </sheetData>

--- a/57.xlsx
+++ b/57.xlsx
@@ -511,7 +511,7 @@
         <v>0.304724782705307</v>
       </c>
       <c r="K2" t="n">
-        <v>2.706360000047425e-05</v>
+        <v>1.223939999999857e-05</v>
       </c>
     </row>
     <row r="3">
@@ -552,7 +552,7 @@
         <v>0.3108069598674774</v>
       </c>
       <c r="K3" t="n">
-        <v>5.6760999996186e-06</v>
+        <v>6.715600000006816e-06</v>
       </c>
     </row>
     <row r="4">
@@ -593,7 +593,7 @@
         <v>0.3064090311527252</v>
       </c>
       <c r="K4" t="n">
-        <v>5.827299999509705e-06</v>
+        <v>6.624199999805569e-06</v>
       </c>
     </row>
     <row r="5">
@@ -634,7 +634,7 @@
         <v>0.3084602057933807</v>
       </c>
       <c r="K5" t="n">
-        <v>5.827799999678973e-06</v>
+        <v>1.576039999963541e-05</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         <v>0.3026606142520905</v>
       </c>
       <c r="K6" t="n">
-        <v>6.675700000414509e-06</v>
+        <v>1.509680000026492e-05</v>
       </c>
     </row>
     <row r="7">
@@ -716,7 +716,7 @@
         <v>0.2876628041267395</v>
       </c>
       <c r="K7" t="n">
-        <v>5.741200000557001e-06</v>
+        <v>1.379929999984597e-05</v>
       </c>
     </row>
     <row r="8">
@@ -757,7 +757,7 @@
         <v>0.281400203704834</v>
       </c>
       <c r="K8" t="n">
-        <v>5.83569999980682e-06</v>
+        <v>1.310730000022886e-05</v>
       </c>
     </row>
     <row r="9">
@@ -798,7 +798,7 @@
         <v>0.2835347056388855</v>
       </c>
       <c r="K9" t="n">
-        <v>6.47690000005241e-06</v>
+        <v>1.299380000000383e-05</v>
       </c>
     </row>
     <row r="10">
@@ -839,7 +839,7 @@
         <v>0.2849827110767365</v>
       </c>
       <c r="K10" t="n">
-        <v>5.565600000409177e-06</v>
+        <v>1.297400000021298e-05</v>
       </c>
     </row>
     <row r="11">
@@ -880,7 +880,7 @@
         <v>0.2848705351352692</v>
       </c>
       <c r="K11" t="n">
-        <v>6.488299999546143e-06</v>
+        <v>1.398699999981545e-05</v>
       </c>
     </row>
     <row r="12">
@@ -921,7 +921,7 @@
         <v>0.3029690682888031</v>
       </c>
       <c r="K12" t="n">
-        <v>6.079000000681844e-06</v>
+        <v>1.434950000020763e-05</v>
       </c>
     </row>
     <row r="13">
@@ -962,7 +962,7 @@
         <v>0.3073286116123199</v>
       </c>
       <c r="K13" t="n">
-        <v>6.391900000380701e-06</v>
+        <v>1.297769999973752e-05</v>
       </c>
     </row>
     <row r="14">
@@ -1003,7 +1003,7 @@
         <v>0.305938184261322</v>
       </c>
       <c r="K14" t="n">
-        <v>5.572699999902397e-06</v>
+        <v>7.286000000021886e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1044,7 +1044,7 @@
         <v>0.3058680295944214</v>
       </c>
       <c r="K15" t="n">
-        <v>5.407399999967311e-06</v>
+        <v>7.967000000007828e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1085,7 +1085,7 @@
         <v>0.3027482926845551</v>
       </c>
       <c r="K16" t="n">
-        <v>5.210200000874465e-06</v>
+        <v>6.815399999595684e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1126,7 +1126,7 @@
         <v>0.3149725496768951</v>
       </c>
       <c r="K17" t="n">
-        <v>9.88590000088152e-06</v>
+        <v>9.298299999954906e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1167,7 +1167,7 @@
         <v>0.3141289055347443</v>
       </c>
       <c r="K18" t="n">
-        <v>8.367300000827526e-06</v>
+        <v>9.537500000078581e-06</v>
       </c>
     </row>
     <row r="19">
@@ -1208,7 +1208,7 @@
         <v>0.3117594718933105</v>
       </c>
       <c r="K19" t="n">
-        <v>7.962699999552569e-06</v>
+        <v>9.874500000023544e-06</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.3145458400249481</v>
       </c>
       <c r="K20" t="n">
-        <v>7.758699999612873e-06</v>
+        <v>2.345719999993889e-05</v>
       </c>
     </row>
     <row r="21">
@@ -1290,7 +1290,7 @@
         <v>0.3127709329128265</v>
       </c>
       <c r="K21" t="n">
-        <v>8.41010000112874e-06</v>
+        <v>9.703700000045501e-06</v>
       </c>
     </row>
     <row r="22">
@@ -1331,7 +1331,7 @@
         <v>0.2798687517642975</v>
       </c>
       <c r="K22" t="n">
-        <v>7.588599999508006e-06</v>
+        <v>9.165500000108295e-06</v>
       </c>
     </row>
     <row r="23">
@@ -1372,7 +1372,7 @@
         <v>0.294763058423996</v>
       </c>
       <c r="K23" t="n">
-        <v>7.538300000305753e-06</v>
+        <v>9.044699999776639e-06</v>
       </c>
     </row>
     <row r="24">
@@ -1413,7 +1413,7 @@
         <v>0.302911102771759</v>
       </c>
       <c r="K24" t="n">
-        <v>7.897899999079527e-06</v>
+        <v>8.347999999841703e-06</v>
       </c>
     </row>
     <row r="25">
@@ -1454,7 +1454,7 @@
         <v>0.2694041430950165</v>
       </c>
       <c r="K25" t="n">
-        <v>7.763600000544101e-06</v>
+        <v>8.982400000149937e-06</v>
       </c>
     </row>
     <row r="26">
@@ -1495,7 +1495,7 @@
         <v>0.2688374519348145</v>
       </c>
       <c r="K26" t="n">
-        <v>8.927400000175112e-06</v>
+        <v>9.641999999985274e-06</v>
       </c>
     </row>
   </sheetData>

--- a/57.xlsx
+++ b/57.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,20 +486,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-21.57 (2.65)</t>
+          <t>-21.57</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1005703210830688</v>
+        <v>0.09434932265430689</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02561863884329796</v>
+        <v>0.02561864013411105</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3766761422157288</v>
+        <v>0.3451693988442421</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03200440853834152</v>
+        <v>0.03200440763123334</v>
       </c>
       <c r="H2" t="n">
         <v>0.966431200504303</v>
@@ -511,7 +511,7 @@
         <v>0.304724782705307</v>
       </c>
       <c r="K2" t="n">
-        <v>1.223939999999857e-05</v>
+        <v>2.026700000010351e-05</v>
       </c>
     </row>
     <row r="3">
@@ -527,20 +527,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-21.60 (2.65)</t>
+          <t>-21.60</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1123339980840683</v>
+        <v>0.09388088473677635</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02597819082438946</v>
+        <v>0.02597818809561431</v>
       </c>
       <c r="F3" t="n">
-        <v>0.363652229309082</v>
+        <v>0.3365442184209824</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03071817383170128</v>
+        <v>0.0307181731145829</v>
       </c>
       <c r="H3" t="n">
         <v>0.969656229019165</v>
@@ -552,7 +552,7 @@
         <v>0.3108069598674774</v>
       </c>
       <c r="K3" t="n">
-        <v>6.715600000006816e-06</v>
+        <v>1.559489999999641e-05</v>
       </c>
     </row>
     <row r="4">
@@ -568,20 +568,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-21.44 (2.66)</t>
+          <t>-21.44</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1082927286624908</v>
+        <v>0.1000077129751444</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02531410567462444</v>
+        <v>0.02531410590931773</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3699852228164673</v>
+        <v>0.3441619935631752</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03190793097019196</v>
+        <v>0.03190793216787279</v>
       </c>
       <c r="H4" t="n">
         <v>0.1327717751264572</v>
@@ -593,7 +593,7 @@
         <v>0.3064090311527252</v>
       </c>
       <c r="K4" t="n">
-        <v>6.624199999805569e-06</v>
+        <v>1.562160000003132e-05</v>
       </c>
     </row>
     <row r="5">
@@ -609,20 +609,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-21.42 (2.66)</t>
+          <t>-21.42</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1196343451738358</v>
+        <v>0.09624408748000861</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02563889697194099</v>
+        <v>0.02563889695331454</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3684929609298706</v>
+        <v>0.3376447867155075</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03090208023786545</v>
+        <v>0.03090207913704216</v>
       </c>
       <c r="H5" t="n">
         <v>0.9691185355186462</v>
@@ -634,7 +634,7 @@
         <v>0.3084602057933807</v>
       </c>
       <c r="K5" t="n">
-        <v>1.576039999963541e-05</v>
+        <v>1.484619999996539e-05</v>
       </c>
     </row>
     <row r="6">
@@ -650,20 +650,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-21.37 (2.62)</t>
+          <t>-21.37</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.117014154791832</v>
+        <v>0.09292872367799282</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02560588344931602</v>
+        <v>0.0256058842279017</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3813428282737732</v>
+        <v>0.3510798379182816</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03301497548818588</v>
+        <v>0.03301497193425894</v>
       </c>
       <c r="H6" t="n">
         <v>0.1357849091291428</v>
@@ -675,7 +675,7 @@
         <v>0.3026606142520905</v>
       </c>
       <c r="K6" t="n">
-        <v>1.509680000026492e-05</v>
+        <v>2.421839999988151e-05</v>
       </c>
     </row>
     <row r="7">
@@ -691,20 +691,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-21.90 (2.68)</t>
+          <t>-21.90</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>37.79097747802734</v>
+        <v>36.67832434463501</v>
       </c>
       <c r="E7" t="n">
-        <v>3.034065723419189</v>
+        <v>3.034065952301026</v>
       </c>
       <c r="F7" t="n">
-        <v>959.1118774414062</v>
+        <v>935.141348022461</v>
       </c>
       <c r="G7" t="n">
-        <v>8.012264251708984</v>
+        <v>8.012263132095336</v>
       </c>
       <c r="H7" t="n">
         <v>0.5832287073135376</v>
@@ -716,7 +716,7 @@
         <v>0.2876628041267395</v>
       </c>
       <c r="K7" t="n">
-        <v>1.379929999984597e-05</v>
+        <v>2.140220000001136e-05</v>
       </c>
     </row>
     <row r="8">
@@ -732,20 +732,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-21.73 (2.66)</t>
+          <t>-21.73</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>38.44820404052734</v>
+        <v>37.48207948684692</v>
       </c>
       <c r="E8" t="n">
-        <v>3.03003978729248</v>
+        <v>3.030039930820465</v>
       </c>
       <c r="F8" t="n">
-        <v>951.8540649414062</v>
+        <v>929.5084318237305</v>
       </c>
       <c r="G8" t="n">
-        <v>8.152113914489746</v>
+        <v>8.152114129543305</v>
       </c>
       <c r="H8" t="n">
         <v>0.5626966953277588</v>
@@ -757,7 +757,7 @@
         <v>0.281400203704834</v>
       </c>
       <c r="K8" t="n">
-        <v>1.310730000022886e-05</v>
+        <v>1.482800000007956e-05</v>
       </c>
     </row>
     <row r="9">
@@ -773,20 +773,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-21.75 (2.67)</t>
+          <t>-21.75</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>38.1599235534668</v>
+        <v>37.27782392120361</v>
       </c>
       <c r="E9" t="n">
-        <v>3.020694732666016</v>
+        <v>3.020694761514664</v>
       </c>
       <c r="F9" t="n">
-        <v>953.0140991210938</v>
+        <v>927.156200378418</v>
       </c>
       <c r="G9" t="n">
-        <v>8.096363067626953</v>
+        <v>8.09636275100708</v>
       </c>
       <c r="H9" t="n">
         <v>0.5651940703392029</v>
@@ -798,7 +798,7 @@
         <v>0.2835347056388855</v>
       </c>
       <c r="K9" t="n">
-        <v>1.299380000000383e-05</v>
+        <v>2.446199999985765e-05</v>
       </c>
     </row>
     <row r="10">
@@ -814,20 +814,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-22.31 (2.63)</t>
+          <t>-22.31</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>38.21701431274414</v>
+        <v>37.2257766456604</v>
       </c>
       <c r="E10" t="n">
-        <v>3.010962247848511</v>
+        <v>3.01096231508255</v>
       </c>
       <c r="F10" t="n">
-        <v>955.25537109375</v>
+        <v>930.6664410400391</v>
       </c>
       <c r="G10" t="n">
-        <v>8.081099510192871</v>
+        <v>8.081100230693817</v>
       </c>
       <c r="H10" t="n">
         <v>0.5666752457618713</v>
@@ -839,7 +839,7 @@
         <v>0.2849827110767365</v>
       </c>
       <c r="K10" t="n">
-        <v>1.297400000021298e-05</v>
+        <v>1.539690000004157e-05</v>
       </c>
     </row>
     <row r="11">
@@ -855,20 +855,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-21.96 (2.66)</t>
+          <t>-21.96</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>38.16988372802734</v>
+        <v>37.20124872970581</v>
       </c>
       <c r="E11" t="n">
-        <v>3.017095327377319</v>
+        <v>3.01709536409378</v>
       </c>
       <c r="F11" t="n">
-        <v>945.5015258789062</v>
+        <v>922.7560665283203</v>
       </c>
       <c r="G11" t="n">
-        <v>8.08076000213623</v>
+        <v>8.080758974075318</v>
       </c>
       <c r="H11" t="n">
         <v>0.5625405311584473</v>
@@ -880,7 +880,7 @@
         <v>0.2848705351352692</v>
       </c>
       <c r="K11" t="n">
-        <v>1.398699999981545e-05</v>
+        <v>1.427489999991849e-05</v>
       </c>
     </row>
     <row r="12">
@@ -896,20 +896,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-23.75 (2.64)</t>
+          <t>-23.75</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>39.31764221191406</v>
+        <v>38.34482963180542</v>
       </c>
       <c r="E12" t="n">
-        <v>2.962957143783569</v>
+        <v>2.962956932783127</v>
       </c>
       <c r="F12" t="n">
-        <v>984.1077880859375</v>
+        <v>938.5292324829102</v>
       </c>
       <c r="G12" t="n">
-        <v>8.326436996459961</v>
+        <v>8.326436245918273</v>
       </c>
       <c r="H12" t="n">
         <v>0.5311014652252197</v>
@@ -921,7 +921,7 @@
         <v>0.3029690682888031</v>
       </c>
       <c r="K12" t="n">
-        <v>1.434950000020763e-05</v>
+        <v>1.898010000013528e-05</v>
       </c>
     </row>
     <row r="13">
@@ -937,20 +937,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-23.88 (2.66)</t>
+          <t>-23.88</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>39.23785400390625</v>
+        <v>38.32909970092773</v>
       </c>
       <c r="E13" t="n">
-        <v>2.96320104598999</v>
+        <v>2.963200966358185</v>
       </c>
       <c r="F13" t="n">
-        <v>980.4300537109375</v>
+        <v>942.3364686279297</v>
       </c>
       <c r="G13" t="n">
-        <v>8.356050491333008</v>
+        <v>8.356051283836365</v>
       </c>
       <c r="H13" t="n">
         <v>0.5334012508392334</v>
@@ -962,7 +962,7 @@
         <v>0.3073286116123199</v>
       </c>
       <c r="K13" t="n">
-        <v>1.297769999973752e-05</v>
+        <v>1.506510000012895e-05</v>
       </c>
     </row>
     <row r="14">
@@ -978,20 +978,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-23.80 (2.65)</t>
+          <t>-23.80</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>39.48330307006836</v>
+        <v>38.50835977554321</v>
       </c>
       <c r="E14" t="n">
-        <v>2.967262506484985</v>
+        <v>2.967262668132782</v>
       </c>
       <c r="F14" t="n">
-        <v>995.008544921875</v>
+        <v>949.3453792724609</v>
       </c>
       <c r="G14" t="n">
-        <v>8.401307106018066</v>
+        <v>8.401307012557984</v>
       </c>
       <c r="H14" t="n">
         <v>0.5297303795814514</v>
@@ -1003,7 +1003,7 @@
         <v>0.305938184261322</v>
       </c>
       <c r="K14" t="n">
-        <v>7.286000000021886e-06</v>
+        <v>1.616549999994277e-05</v>
       </c>
     </row>
     <row r="15">
@@ -1019,20 +1019,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-23.85 (2.66)</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>39.12985992431641</v>
+        <v>38.15680184936524</v>
       </c>
       <c r="E15" t="n">
-        <v>2.958388090133667</v>
+        <v>2.958388218402863</v>
       </c>
       <c r="F15" t="n">
-        <v>980.7908325195312</v>
+        <v>932.182260131836</v>
       </c>
       <c r="G15" t="n">
-        <v>8.282486915588379</v>
+        <v>8.282486514091492</v>
       </c>
       <c r="H15" t="n">
         <v>0.5341669917106628</v>
@@ -1044,7 +1044,7 @@
         <v>0.3058680295944214</v>
       </c>
       <c r="K15" t="n">
-        <v>7.967000000007828e-06</v>
+        <v>1.686130000007324e-05</v>
       </c>
     </row>
     <row r="16">
@@ -1060,20 +1060,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-23.61 (2.66)</t>
+          <t>-23.61</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>39.22180938720703</v>
+        <v>38.29413411712647</v>
       </c>
       <c r="E16" t="n">
-        <v>2.961922645568848</v>
+        <v>2.961922732591629</v>
       </c>
       <c r="F16" t="n">
-        <v>980.8865966796875</v>
+        <v>939.2883869628906</v>
       </c>
       <c r="G16" t="n">
-        <v>8.327680587768555</v>
+        <v>8.327680652618408</v>
       </c>
       <c r="H16" t="n">
         <v>0.5311251282691956</v>
@@ -1085,7 +1085,7 @@
         <v>0.3027482926845551</v>
       </c>
       <c r="K16" t="n">
-        <v>6.815399999595684e-06</v>
+        <v>1.621250000016517e-05</v>
       </c>
     </row>
     <row r="17">
@@ -1101,20 +1101,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-18.52 (2.72)</t>
+          <t>-18.52</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.07514205574989319</v>
+        <v>0.06072998848930002</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02299807965755463</v>
+        <v>0.0229980776719749</v>
       </c>
       <c r="F17" t="n">
-        <v>0.005046725273132324</v>
+        <v>0.003742030739784241</v>
       </c>
       <c r="G17" t="n">
-        <v>1.595467801962513e-05</v>
+        <v>1.595467791321426e-05</v>
       </c>
       <c r="H17" t="n">
         <v>0.0548088327050209</v>
@@ -1126,7 +1126,7 @@
         <v>0.3149725496768951</v>
       </c>
       <c r="K17" t="n">
-        <v>9.298299999954906e-06</v>
+        <v>2.788949999990109e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1142,20 +1142,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-18.24 (2.73)</t>
+          <t>-18.24</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.07990183681249619</v>
+        <v>0.06529260030388832</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02297288365662098</v>
+        <v>0.02297288282960653</v>
       </c>
       <c r="F18" t="n">
-        <v>0.005101442337036133</v>
+        <v>0.003535274505615234</v>
       </c>
       <c r="G18" t="n">
-        <v>1.50457417475991e-05</v>
+        <v>1.504573960301059e-05</v>
       </c>
       <c r="H18" t="n">
         <v>0.05438490584492683</v>
@@ -1167,7 +1167,7 @@
         <v>0.3141289055347443</v>
       </c>
       <c r="K18" t="n">
-        <v>9.537500000078581e-06</v>
+        <v>2.322320000007494e-05</v>
       </c>
     </row>
     <row r="19">
@@ -1183,20 +1183,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-18.57 (2.68)</t>
+          <t>-18.57</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.07461848855018616</v>
+        <v>0.06389518796652556</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02308282814919949</v>
+        <v>0.02308282779343426</v>
       </c>
       <c r="F19" t="n">
-        <v>0.004960298538208008</v>
+        <v>0.003997717022895813</v>
       </c>
       <c r="G19" t="n">
-        <v>1.653458093642257e-05</v>
+        <v>1.653458106102334e-05</v>
       </c>
       <c r="H19" t="n">
         <v>0.05574209243059158</v>
@@ -1208,7 +1208,7 @@
         <v>0.3117594718933105</v>
       </c>
       <c r="K19" t="n">
-        <v>9.874500000023544e-06</v>
+        <v>1.986349999992853e-05</v>
       </c>
     </row>
     <row r="20">
@@ -1224,20 +1224,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-18.42 (2.69)</t>
+          <t>-18.42</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.07324337214231491</v>
+        <v>0.06355301559343934</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0232883132994175</v>
+        <v>0.02328831494040787</v>
       </c>
       <c r="F20" t="n">
-        <v>0.004958510398864746</v>
+        <v>0.003874084949493408</v>
       </c>
       <c r="G20" t="n">
-        <v>1.652943319641054e-05</v>
+        <v>1.652943236513238e-05</v>
       </c>
       <c r="H20" t="n">
         <v>0.0551995262503624</v>
@@ -1249,7 +1249,7 @@
         <v>0.3145458400249481</v>
       </c>
       <c r="K20" t="n">
-        <v>2.345719999993889e-05</v>
+        <v>1.924559999997655e-05</v>
       </c>
     </row>
     <row r="21">
@@ -1265,20 +1265,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-18.50 (2.67)</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.07633413374423981</v>
+        <v>0.06380707132443786</v>
       </c>
       <c r="E21" t="n">
-        <v>0.02324997074902058</v>
+        <v>0.02324996946938336</v>
       </c>
       <c r="F21" t="n">
-        <v>0.005114316940307617</v>
+        <v>0.003707248449325561</v>
       </c>
       <c r="G21" t="n">
-        <v>1.581008837092668e-05</v>
+        <v>1.581008816719987e-05</v>
       </c>
       <c r="H21" t="n">
         <v>0.05478144809603691</v>
@@ -1290,7 +1290,7 @@
         <v>0.3127709329128265</v>
       </c>
       <c r="K21" t="n">
-        <v>9.703700000045501e-06</v>
+        <v>2.94111000000612e-05</v>
       </c>
     </row>
     <row r="22">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>8.54 (2.31)</t>
+          <t>8.54</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.25540292263031</v>
+        <v>1.069020014822483</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1131935641169548</v>
+        <v>0.1131935617104173</v>
       </c>
       <c r="F22" t="n">
-        <v>0.003107786178588867</v>
+        <v>0.002146059036254883</v>
       </c>
       <c r="G22" t="n">
-        <v>4.645149601856247e-06</v>
+        <v>4.645149432690232e-06</v>
       </c>
       <c r="H22" t="n">
         <v>0.04186482727527618</v>
@@ -1331,7 +1331,7 @@
         <v>0.2798687517642975</v>
       </c>
       <c r="K22" t="n">
-        <v>9.165500000108295e-06</v>
+        <v>2.030119999994895e-05</v>
       </c>
     </row>
     <row r="23">
@@ -1347,20 +1347,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9.40 (2.33)</t>
+          <t>9.40</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1.022862672805786</v>
+        <v>0.9600494065880776</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1552429050207138</v>
+        <v>0.1552429073750973</v>
       </c>
       <c r="F23" t="n">
-        <v>0.007849574089050293</v>
+        <v>0.006255125045776367</v>
       </c>
       <c r="G23" t="n">
-        <v>3.04658169625327e-05</v>
+        <v>3.046581961825723e-05</v>
       </c>
       <c r="H23" t="n">
         <v>0.05201252922415733</v>
@@ -1372,7 +1372,7 @@
         <v>0.294763058423996</v>
       </c>
       <c r="K23" t="n">
-        <v>9.044699999776639e-06</v>
+        <v>2.029670000001715e-05</v>
       </c>
     </row>
     <row r="24">
@@ -1388,20 +1388,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>7.42 (2.28)</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1.149510741233826</v>
+        <v>0.9546271737813949</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1058946177363396</v>
+        <v>0.1058946109116077</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01351070404052734</v>
+        <v>0.01004328989982605</v>
       </c>
       <c r="G24" t="n">
-        <v>3.617384209064767e-05</v>
+        <v>3.617384266181034e-05</v>
       </c>
       <c r="H24" t="n">
         <v>0.05830847471952438</v>
@@ -1413,7 +1413,7 @@
         <v>0.302911102771759</v>
       </c>
       <c r="K24" t="n">
-        <v>8.347999999841703e-06</v>
+        <v>1.993349999997917e-05</v>
       </c>
     </row>
     <row r="25">
@@ -1429,20 +1429,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>12.54 (2.40)</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.8676587343215942</v>
+        <v>0.7812392020821571</v>
       </c>
       <c r="E25" t="n">
-        <v>0.09677117317914963</v>
+        <v>0.09677117650210858</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02125382423400879</v>
+        <v>0.01393528139591217</v>
       </c>
       <c r="G25" t="n">
-        <v>6.544401549035683e-05</v>
+        <v>6.544401349674444e-05</v>
       </c>
       <c r="H25" t="n">
         <v>0.06584927439689636</v>
@@ -1454,7 +1454,7 @@
         <v>0.2694041430950165</v>
       </c>
       <c r="K25" t="n">
-        <v>8.982400000149937e-06</v>
+        <v>3.146919999994679e-05</v>
       </c>
     </row>
     <row r="26">
@@ -1470,14 +1470,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>8.96 (2.32)</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.8835476040840149</v>
+        <v>0.829081823527813</v>
       </c>
       <c r="E26" t="n">
-        <v>0.09112653881311417</v>
+        <v>0.09112653527408839</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1495,7 +1495,212 @@
         <v>0.2688374519348145</v>
       </c>
       <c r="K26" t="n">
-        <v>9.641999999985274e-06</v>
+        <v>2.139940000006391e-05</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ablated PINN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Run 1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>-330.00</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.1566219767332077</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.02684792033210397</v>
+      </c>
+      <c r="F27" t="n">
+        <v>17.60419565582275</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.362533863991499</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.101846694946289</v>
+      </c>
+      <c r="I27" t="n">
+        <v>12.13983631134033</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.37524151802063</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.609890000008818e-05</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ablated PINN</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Run 2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>-328.60</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.1763519300222397</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.028098428029567</v>
+      </c>
+      <c r="F28" t="n">
+        <v>17.55601633644104</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.3579410746395588</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.094076871871948</v>
+      </c>
+      <c r="I28" t="n">
+        <v>12.10176372528076</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.378463745117188</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.178800000002411e-05</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ablated PINN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Run 3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>-331.84</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.1424202823936939</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.02639745533652604</v>
+      </c>
+      <c r="F29" t="n">
+        <v>17.65824348449707</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.3668395908474922</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.109405018389225</v>
+      </c>
+      <c r="I29" t="n">
+        <v>12.1846752166748</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.375186085700989</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.213419999999132e-05</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ablated PINN</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Run 4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>-327.93</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.1455211078673601</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.02826853665336966</v>
+      </c>
+      <c r="F30" t="n">
+        <v>17.50471514892578</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.3547890853285789</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.09808075428009</v>
+      </c>
+      <c r="I30" t="n">
+        <v>12.06720542907715</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.369550943374634</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1.31984999998167e-05</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ablated PINN</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Run 5</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>-284.20</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.08124188476800918</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.02001002448424697</v>
+      </c>
+      <c r="F31" t="n">
+        <v>16.4855033416748</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.3871498747169971</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.9303419589996338</v>
+      </c>
+      <c r="I31" t="n">
+        <v>11.24994659423828</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.835822105407715</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.115709999999126e-05</v>
       </c>
     </row>
   </sheetData>

--- a/57.xlsx
+++ b/57.xlsx
@@ -486,20 +486,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-21.57</t>
+          <t>-21.57 (2.65)</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.09434932265430689</v>
+        <v>0.1005703210830688</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02561864013411105</v>
+        <v>0.02561863884329796</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3451693988442421</v>
+        <v>0.3766761422157288</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03200440763123334</v>
+        <v>0.03200440853834152</v>
       </c>
       <c r="H2" t="n">
         <v>0.966431200504303</v>
@@ -511,7 +511,7 @@
         <v>0.304724782705307</v>
       </c>
       <c r="K2" t="n">
-        <v>2.026700000010351e-05</v>
+        <v>1.141350000398234e-05</v>
       </c>
     </row>
     <row r="3">
@@ -527,20 +527,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-21.60</t>
+          <t>-21.60 (2.65)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.09388088473677635</v>
+        <v>0.1123339980840683</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02597818809561431</v>
+        <v>0.02597819082438946</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3365442184209824</v>
+        <v>0.363652229309082</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0307181731145829</v>
+        <v>0.03071817383170128</v>
       </c>
       <c r="H3" t="n">
         <v>0.969656229019165</v>
@@ -552,7 +552,7 @@
         <v>0.3108069598674774</v>
       </c>
       <c r="K3" t="n">
-        <v>1.559489999999641e-05</v>
+        <v>6.96839999727672e-06</v>
       </c>
     </row>
     <row r="4">
@@ -568,20 +568,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-21.44</t>
+          <t>-21.44 (2.66)</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1000077129751444</v>
+        <v>0.1082927286624908</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02531410590931773</v>
+        <v>0.02531410567462444</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3441619935631752</v>
+        <v>0.3699852228164673</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03190793216787279</v>
+        <v>0.03190793097019196</v>
       </c>
       <c r="H4" t="n">
         <v>0.1327717751264572</v>
@@ -593,7 +593,7 @@
         <v>0.3064090311527252</v>
       </c>
       <c r="K4" t="n">
-        <v>1.562160000003132e-05</v>
+        <v>8.609299999079667e-06</v>
       </c>
     </row>
     <row r="5">
@@ -609,20 +609,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-21.42</t>
+          <t>-21.42 (2.66)</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.09624408748000861</v>
+        <v>0.1196343451738358</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02563889695331454</v>
+        <v>0.02563889697194099</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3376447867155075</v>
+        <v>0.3684929609298706</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03090207913704216</v>
+        <v>0.03090208023786545</v>
       </c>
       <c r="H5" t="n">
         <v>0.9691185355186462</v>
@@ -634,7 +634,7 @@
         <v>0.3084602057933807</v>
       </c>
       <c r="K5" t="n">
-        <v>1.484619999996539e-05</v>
+        <v>7.053499997709878e-06</v>
       </c>
     </row>
     <row r="6">
@@ -650,20 +650,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-21.37</t>
+          <t>-21.37 (2.62)</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.09292872367799282</v>
+        <v>0.117014154791832</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0256058842279017</v>
+        <v>0.02560588344931602</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3510798379182816</v>
+        <v>0.3813428282737732</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03301497193425894</v>
+        <v>0.03301497548818588</v>
       </c>
       <c r="H6" t="n">
         <v>0.1357849091291428</v>
@@ -675,7 +675,7 @@
         <v>0.3026606142520905</v>
       </c>
       <c r="K6" t="n">
-        <v>2.421839999988151e-05</v>
+        <v>6.890800003020559e-06</v>
       </c>
     </row>
     <row r="7">
@@ -691,20 +691,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-21.90</t>
+          <t>-21.90 (2.68)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>36.67832434463501</v>
+        <v>37.79097747802734</v>
       </c>
       <c r="E7" t="n">
-        <v>3.034065952301026</v>
+        <v>3.034065723419189</v>
       </c>
       <c r="F7" t="n">
-        <v>935.141348022461</v>
+        <v>959.1118774414062</v>
       </c>
       <c r="G7" t="n">
-        <v>8.012263132095336</v>
+        <v>8.012264251708984</v>
       </c>
       <c r="H7" t="n">
         <v>0.5832287073135376</v>
@@ -716,7 +716,7 @@
         <v>0.2876628041267395</v>
       </c>
       <c r="K7" t="n">
-        <v>2.140220000001136e-05</v>
+        <v>5.949300000793301e-06</v>
       </c>
     </row>
     <row r="8">
@@ -732,20 +732,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-21.73</t>
+          <t>-21.73 (2.66)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>37.48207948684692</v>
+        <v>38.44820404052734</v>
       </c>
       <c r="E8" t="n">
-        <v>3.030039930820465</v>
+        <v>3.03003978729248</v>
       </c>
       <c r="F8" t="n">
-        <v>929.5084318237305</v>
+        <v>951.8540649414062</v>
       </c>
       <c r="G8" t="n">
-        <v>8.152114129543305</v>
+        <v>8.152113914489746</v>
       </c>
       <c r="H8" t="n">
         <v>0.5626966953277588</v>
@@ -757,7 +757,7 @@
         <v>0.281400203704834</v>
       </c>
       <c r="K8" t="n">
-        <v>1.482800000007956e-05</v>
+        <v>6.471200002124533e-06</v>
       </c>
     </row>
     <row r="9">
@@ -773,20 +773,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-21.75</t>
+          <t>-21.75 (2.67)</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>37.27782392120361</v>
+        <v>38.1599235534668</v>
       </c>
       <c r="E9" t="n">
-        <v>3.020694761514664</v>
+        <v>3.020694732666016</v>
       </c>
       <c r="F9" t="n">
-        <v>927.156200378418</v>
+        <v>953.0140991210938</v>
       </c>
       <c r="G9" t="n">
-        <v>8.09636275100708</v>
+        <v>8.096363067626953</v>
       </c>
       <c r="H9" t="n">
         <v>0.5651940703392029</v>
@@ -798,7 +798,7 @@
         <v>0.2835347056388855</v>
       </c>
       <c r="K9" t="n">
-        <v>2.446199999985765e-05</v>
+        <v>7.677699999476318e-06</v>
       </c>
     </row>
     <row r="10">
@@ -814,20 +814,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-22.31</t>
+          <t>-22.31 (2.63)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>37.2257766456604</v>
+        <v>38.21701431274414</v>
       </c>
       <c r="E10" t="n">
-        <v>3.01096231508255</v>
+        <v>3.010962247848511</v>
       </c>
       <c r="F10" t="n">
-        <v>930.6664410400391</v>
+        <v>955.25537109375</v>
       </c>
       <c r="G10" t="n">
-        <v>8.081100230693817</v>
+        <v>8.081099510192871</v>
       </c>
       <c r="H10" t="n">
         <v>0.5666752457618713</v>
@@ -839,7 +839,7 @@
         <v>0.2849827110767365</v>
       </c>
       <c r="K10" t="n">
-        <v>1.539690000004157e-05</v>
+        <v>6.067599999369122e-06</v>
       </c>
     </row>
     <row r="11">
@@ -855,20 +855,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-21.96</t>
+          <t>-21.96 (2.66)</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>37.20124872970581</v>
+        <v>38.16988372802734</v>
       </c>
       <c r="E11" t="n">
-        <v>3.01709536409378</v>
+        <v>3.017095327377319</v>
       </c>
       <c r="F11" t="n">
-        <v>922.7560665283203</v>
+        <v>945.5015258789062</v>
       </c>
       <c r="G11" t="n">
-        <v>8.080758974075318</v>
+        <v>8.08076000213623</v>
       </c>
       <c r="H11" t="n">
         <v>0.5625405311584473</v>
@@ -880,7 +880,7 @@
         <v>0.2848705351352692</v>
       </c>
       <c r="K11" t="n">
-        <v>1.427489999991849e-05</v>
+        <v>6.383100000675768e-06</v>
       </c>
     </row>
     <row r="12">
@@ -896,20 +896,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-23.75</t>
+          <t>-23.75 (2.64)</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>38.34482963180542</v>
+        <v>39.31764221191406</v>
       </c>
       <c r="E12" t="n">
-        <v>2.962956932783127</v>
+        <v>2.962957143783569</v>
       </c>
       <c r="F12" t="n">
-        <v>938.5292324829102</v>
+        <v>984.1077880859375</v>
       </c>
       <c r="G12" t="n">
-        <v>8.326436245918273</v>
+        <v>8.326436996459961</v>
       </c>
       <c r="H12" t="n">
         <v>0.5311014652252197</v>
@@ -921,7 +921,7 @@
         <v>0.3029690682888031</v>
       </c>
       <c r="K12" t="n">
-        <v>1.898010000013528e-05</v>
+        <v>7.781699998304247e-06</v>
       </c>
     </row>
     <row r="13">
@@ -937,20 +937,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-23.88</t>
+          <t>-23.88 (2.66)</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>38.32909970092773</v>
+        <v>39.23785400390625</v>
       </c>
       <c r="E13" t="n">
-        <v>2.963200966358185</v>
+        <v>2.96320104598999</v>
       </c>
       <c r="F13" t="n">
-        <v>942.3364686279297</v>
+        <v>980.4300537109375</v>
       </c>
       <c r="G13" t="n">
-        <v>8.356051283836365</v>
+        <v>8.356050491333008</v>
       </c>
       <c r="H13" t="n">
         <v>0.5334012508392334</v>
@@ -962,7 +962,7 @@
         <v>0.3073286116123199</v>
       </c>
       <c r="K13" t="n">
-        <v>1.506510000012895e-05</v>
+        <v>6.074099997931626e-06</v>
       </c>
     </row>
     <row r="14">
@@ -978,20 +978,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-23.80</t>
+          <t>-23.80 (2.65)</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>38.50835977554321</v>
+        <v>39.48330307006836</v>
       </c>
       <c r="E14" t="n">
-        <v>2.967262668132782</v>
+        <v>2.967262506484985</v>
       </c>
       <c r="F14" t="n">
-        <v>949.3453792724609</v>
+        <v>995.008544921875</v>
       </c>
       <c r="G14" t="n">
-        <v>8.401307012557984</v>
+        <v>8.401307106018066</v>
       </c>
       <c r="H14" t="n">
         <v>0.5297303795814514</v>
@@ -1003,7 +1003,7 @@
         <v>0.305938184261322</v>
       </c>
       <c r="K14" t="n">
-        <v>1.616549999994277e-05</v>
+        <v>6.256499997107312e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1019,20 +1019,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-23.85</t>
+          <t>-23.85 (2.66)</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>38.15680184936524</v>
+        <v>39.12985992431641</v>
       </c>
       <c r="E15" t="n">
-        <v>2.958388218402863</v>
+        <v>2.958388090133667</v>
       </c>
       <c r="F15" t="n">
-        <v>932.182260131836</v>
+        <v>980.7908325195312</v>
       </c>
       <c r="G15" t="n">
-        <v>8.282486514091492</v>
+        <v>8.282486915588379</v>
       </c>
       <c r="H15" t="n">
         <v>0.5341669917106628</v>
@@ -1044,7 +1044,7 @@
         <v>0.3058680295944214</v>
       </c>
       <c r="K15" t="n">
-        <v>1.686130000007324e-05</v>
+        <v>6.426600004488137e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1060,20 +1060,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-23.61</t>
+          <t>-23.61 (2.66)</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>38.29413411712647</v>
+        <v>39.22180938720703</v>
       </c>
       <c r="E16" t="n">
-        <v>2.961922732591629</v>
+        <v>2.961922645568848</v>
       </c>
       <c r="F16" t="n">
-        <v>939.2883869628906</v>
+        <v>980.8865966796875</v>
       </c>
       <c r="G16" t="n">
-        <v>8.327680652618408</v>
+        <v>8.327680587768555</v>
       </c>
       <c r="H16" t="n">
         <v>0.5311251282691956</v>
@@ -1085,7 +1085,7 @@
         <v>0.3027482926845551</v>
       </c>
       <c r="K16" t="n">
-        <v>1.621250000016517e-05</v>
+        <v>6.700300000375137e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1101,20 +1101,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-18.52</t>
+          <t>-18.52 (2.72)</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.06072998848930002</v>
+        <v>0.07514205574989319</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0229980776719749</v>
+        <v>0.02299807965755463</v>
       </c>
       <c r="F17" t="n">
-        <v>0.003742030739784241</v>
+        <v>0.005046725273132324</v>
       </c>
       <c r="G17" t="n">
-        <v>1.595467791321426e-05</v>
+        <v>1.595467801962513e-05</v>
       </c>
       <c r="H17" t="n">
         <v>0.0548088327050209</v>
@@ -1126,7 +1126,7 @@
         <v>0.3149725496768951</v>
       </c>
       <c r="K17" t="n">
-        <v>2.788949999990109e-05</v>
+        <v>9.185999995679595e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1142,20 +1142,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-18.24</t>
+          <t>-18.24 (2.73)</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.06529260030388832</v>
+        <v>0.07990183681249619</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02297288282960653</v>
+        <v>0.02297288365662098</v>
       </c>
       <c r="F18" t="n">
-        <v>0.003535274505615234</v>
+        <v>0.005101442337036133</v>
       </c>
       <c r="G18" t="n">
-        <v>1.504573960301059e-05</v>
+        <v>1.50457417475991e-05</v>
       </c>
       <c r="H18" t="n">
         <v>0.05438490584492683</v>
@@ -1167,7 +1167,7 @@
         <v>0.3141289055347443</v>
       </c>
       <c r="K18" t="n">
-        <v>2.322320000007494e-05</v>
+        <v>8.90600000275299e-06</v>
       </c>
     </row>
     <row r="19">
@@ -1183,20 +1183,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-18.57</t>
+          <t>-18.57 (2.68)</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.06389518796652556</v>
+        <v>0.07461848855018616</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02308282779343426</v>
+        <v>0.02308282814919949</v>
       </c>
       <c r="F19" t="n">
-        <v>0.003997717022895813</v>
+        <v>0.004960298538208008</v>
       </c>
       <c r="G19" t="n">
-        <v>1.653458106102334e-05</v>
+        <v>1.653458093642257e-05</v>
       </c>
       <c r="H19" t="n">
         <v>0.05574209243059158</v>
@@ -1208,7 +1208,7 @@
         <v>0.3117594718933105</v>
       </c>
       <c r="K19" t="n">
-        <v>1.986349999992853e-05</v>
+        <v>8.867500000633299e-06</v>
       </c>
     </row>
     <row r="20">
@@ -1224,20 +1224,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-18.42</t>
+          <t>-18.42 (2.69)</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.06355301559343934</v>
+        <v>0.07324337214231491</v>
       </c>
       <c r="E20" t="n">
-        <v>0.02328831494040787</v>
+        <v>0.0232883132994175</v>
       </c>
       <c r="F20" t="n">
-        <v>0.003874084949493408</v>
+        <v>0.004958510398864746</v>
       </c>
       <c r="G20" t="n">
-        <v>1.652943236513238e-05</v>
+        <v>1.652943319641054e-05</v>
       </c>
       <c r="H20" t="n">
         <v>0.0551995262503624</v>
@@ -1249,7 +1249,7 @@
         <v>0.3145458400249481</v>
       </c>
       <c r="K20" t="n">
-        <v>1.924559999997655e-05</v>
+        <v>9.264899999834597e-06</v>
       </c>
     </row>
     <row r="21">
@@ -1265,20 +1265,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-18.50</t>
+          <t>-18.50 (2.67)</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.06380707132443786</v>
+        <v>0.07633413374423981</v>
       </c>
       <c r="E21" t="n">
-        <v>0.02324996946938336</v>
+        <v>0.02324997074902058</v>
       </c>
       <c r="F21" t="n">
-        <v>0.003707248449325561</v>
+        <v>0.005114316940307617</v>
       </c>
       <c r="G21" t="n">
-        <v>1.581008816719987e-05</v>
+        <v>1.581008837092668e-05</v>
       </c>
       <c r="H21" t="n">
         <v>0.05478144809603691</v>
@@ -1290,7 +1290,7 @@
         <v>0.3127709329128265</v>
       </c>
       <c r="K21" t="n">
-        <v>2.94111000000612e-05</v>
+        <v>8.950600000389386e-06</v>
       </c>
     </row>
     <row r="22">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>8.54 (2.31)</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.069020014822483</v>
+        <v>1.25540292263031</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1131935617104173</v>
+        <v>0.1131935641169548</v>
       </c>
       <c r="F22" t="n">
-        <v>0.002146059036254883</v>
+        <v>0.003107786178588867</v>
       </c>
       <c r="G22" t="n">
-        <v>4.645149432690232e-06</v>
+        <v>4.645149601856247e-06</v>
       </c>
       <c r="H22" t="n">
         <v>0.04186482727527618</v>
@@ -1331,7 +1331,7 @@
         <v>0.2798687517642975</v>
       </c>
       <c r="K22" t="n">
-        <v>2.030119999994895e-05</v>
+        <v>9.724899995489977e-06</v>
       </c>
     </row>
     <row r="23">
@@ -1347,20 +1347,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9.40</t>
+          <t>9.40 (2.33)</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.9600494065880776</v>
+        <v>1.022862672805786</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1552429073750973</v>
+        <v>0.1552429050207138</v>
       </c>
       <c r="F23" t="n">
-        <v>0.006255125045776367</v>
+        <v>0.007849574089050293</v>
       </c>
       <c r="G23" t="n">
-        <v>3.046581961825723e-05</v>
+        <v>3.04658169625327e-05</v>
       </c>
       <c r="H23" t="n">
         <v>0.05201252922415733</v>
@@ -1372,7 +1372,7 @@
         <v>0.294763058423996</v>
       </c>
       <c r="K23" t="n">
-        <v>2.029670000001715e-05</v>
+        <v>1.957930000207852e-05</v>
       </c>
     </row>
     <row r="24">
@@ -1388,20 +1388,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>7.42 (2.28)</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.9546271737813949</v>
+        <v>1.149510741233826</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1058946109116077</v>
+        <v>0.1058946177363396</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01004328989982605</v>
+        <v>0.01351070404052734</v>
       </c>
       <c r="G24" t="n">
-        <v>3.617384266181034e-05</v>
+        <v>3.617384209064767e-05</v>
       </c>
       <c r="H24" t="n">
         <v>0.05830847471952438</v>
@@ -1413,7 +1413,7 @@
         <v>0.302911102771759</v>
       </c>
       <c r="K24" t="n">
-        <v>1.993349999997917e-05</v>
+        <v>8.988399997178932e-06</v>
       </c>
     </row>
     <row r="25">
@@ -1429,20 +1429,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>12.54 (2.40)</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.7812392020821571</v>
+        <v>0.8676587343215942</v>
       </c>
       <c r="E25" t="n">
-        <v>0.09677117650210858</v>
+        <v>0.09677117317914963</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01393528139591217</v>
+        <v>0.02125382423400879</v>
       </c>
       <c r="G25" t="n">
-        <v>6.544401349674444e-05</v>
+        <v>6.544401549035683e-05</v>
       </c>
       <c r="H25" t="n">
         <v>0.06584927439689636</v>
@@ -1454,7 +1454,7 @@
         <v>0.2694041430950165</v>
       </c>
       <c r="K25" t="n">
-        <v>3.146919999994679e-05</v>
+        <v>8.920000000216533e-06</v>
       </c>
     </row>
     <row r="26">
@@ -1470,14 +1470,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>8.96 (2.32)</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.829081823527813</v>
+        <v>0.8835476040840149</v>
       </c>
       <c r="E26" t="n">
-        <v>0.09112653527408839</v>
+        <v>0.09112653881311417</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0.2688374519348145</v>
       </c>
       <c r="K26" t="n">
-        <v>2.139940000006391e-05</v>
+        <v>1.131120000354713e-05</v>
       </c>
     </row>
     <row r="27">
@@ -1511,20 +1511,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-330.00</t>
+          <t>-330.00 (5.07)</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.1566219767332077</v>
+        <v>0.1662453711032867</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02684792033210397</v>
+        <v>0.02684792131185532</v>
       </c>
       <c r="F27" t="n">
-        <v>17.60419565582275</v>
+        <v>17.7396240234375</v>
       </c>
       <c r="G27" t="n">
-        <v>0.362533863991499</v>
+        <v>0.3625338971614838</v>
       </c>
       <c r="H27" t="n">
         <v>1.101846694946289</v>
@@ -1536,7 +1536,7 @@
         <v>1.37524151802063</v>
       </c>
       <c r="K27" t="n">
-        <v>1.609890000008818e-05</v>
+        <v>5.481599997438025e-06</v>
       </c>
     </row>
     <row r="28">
@@ -1552,20 +1552,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-328.60</t>
+          <t>-328.60 (5.01)</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.1763519300222397</v>
+        <v>0.1961507499217987</v>
       </c>
       <c r="E28" t="n">
-        <v>0.028098428029567</v>
+        <v>0.02809842675924301</v>
       </c>
       <c r="F28" t="n">
-        <v>17.55601633644104</v>
+        <v>17.73380661010742</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3579410746395588</v>
+        <v>0.3579410910606384</v>
       </c>
       <c r="H28" t="n">
         <v>1.094076871871948</v>
@@ -1577,7 +1577,7 @@
         <v>1.378463745117188</v>
       </c>
       <c r="K28" t="n">
-        <v>1.178800000002411e-05</v>
+        <v>5.754600002546795e-06</v>
       </c>
     </row>
     <row r="29">
@@ -1593,20 +1593,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-331.84</t>
+          <t>-331.84 (5.18)</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.1424202823936939</v>
+        <v>0.1567540913820267</v>
       </c>
       <c r="E29" t="n">
-        <v>0.02639745533652604</v>
+        <v>0.0263974517583847</v>
       </c>
       <c r="F29" t="n">
-        <v>17.65824348449707</v>
+        <v>17.76790618896484</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3668395908474922</v>
+        <v>0.3668395578861237</v>
       </c>
       <c r="H29" t="n">
         <v>0.109405018389225</v>
@@ -1618,7 +1618,7 @@
         <v>1.375186085700989</v>
       </c>
       <c r="K29" t="n">
-        <v>1.213419999999132e-05</v>
+        <v>5.73150000127498e-06</v>
       </c>
     </row>
     <row r="30">
@@ -1634,20 +1634,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-327.93</t>
+          <t>-327.93 (5.07)</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.1455211078673601</v>
+        <v>0.2222423553466797</v>
       </c>
       <c r="E30" t="n">
-        <v>0.02826853665336966</v>
+        <v>0.02826853841543198</v>
       </c>
       <c r="F30" t="n">
-        <v>17.50471514892578</v>
+        <v>17.66987228393555</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3547890853285789</v>
+        <v>0.3547891080379486</v>
       </c>
       <c r="H30" t="n">
         <v>1.09808075428009</v>
@@ -1659,7 +1659,7 @@
         <v>1.369550943374634</v>
       </c>
       <c r="K30" t="n">
-        <v>1.31984999998167e-05</v>
+        <v>5.701099995349068e-06</v>
       </c>
     </row>
     <row r="31">
@@ -1675,20 +1675,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-284.20</t>
+          <t>-284.20 (4.19)</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.08124188476800918</v>
+        <v>0.1142737120389938</v>
       </c>
       <c r="E31" t="n">
-        <v>0.02001002448424697</v>
+        <v>0.02001002244651318</v>
       </c>
       <c r="F31" t="n">
-        <v>16.4855033416748</v>
+        <v>16.6176586151123</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3871498747169971</v>
+        <v>0.3871499001979828</v>
       </c>
       <c r="H31" t="n">
         <v>0.9303419589996338</v>
@@ -1700,7 +1700,7 @@
         <v>2.835822105407715</v>
       </c>
       <c r="K31" t="n">
-        <v>1.115709999999126e-05</v>
+        <v>6.78679999691667e-06</v>
       </c>
     </row>
   </sheetData>

--- a/57.xlsx
+++ b/57.xlsx
@@ -486,20 +486,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-21.57 (2.65)</t>
+          <t>-21.57</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1005703210830688</v>
+        <v>0.09434932265430689</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02561863884329796</v>
+        <v>0.02561864013411105</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3766761422157288</v>
+        <v>0.3451693988442421</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03200440853834152</v>
+        <v>0.03200440763123334</v>
       </c>
       <c r="H2" t="n">
         <v>0.966431200504303</v>
@@ -511,7 +511,7 @@
         <v>0.304724782705307</v>
       </c>
       <c r="K2" t="n">
-        <v>1.141350000398234e-05</v>
+        <v>1.15081000039936e-05</v>
       </c>
     </row>
     <row r="3">
@@ -527,20 +527,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-21.60 (2.65)</t>
+          <t>-21.60</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1123339980840683</v>
+        <v>0.09388088473677635</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02597819082438946</v>
+        <v>0.02597818809561431</v>
       </c>
       <c r="F3" t="n">
-        <v>0.363652229309082</v>
+        <v>0.3365442184209824</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03071817383170128</v>
+        <v>0.0307181731145829</v>
       </c>
       <c r="H3" t="n">
         <v>0.969656229019165</v>
@@ -552,7 +552,7 @@
         <v>0.3108069598674774</v>
       </c>
       <c r="K3" t="n">
-        <v>6.96839999727672e-06</v>
+        <v>7.162000001699198e-06</v>
       </c>
     </row>
     <row r="4">
@@ -568,20 +568,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-21.44 (2.66)</t>
+          <t>-21.44</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1082927286624908</v>
+        <v>0.1000077129751444</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02531410567462444</v>
+        <v>0.02531410590931773</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3699852228164673</v>
+        <v>0.3441619935631752</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03190793097019196</v>
+        <v>0.03190793216787279</v>
       </c>
       <c r="H4" t="n">
         <v>0.1327717751264572</v>
@@ -593,7 +593,7 @@
         <v>0.3064090311527252</v>
       </c>
       <c r="K4" t="n">
-        <v>8.609299999079667e-06</v>
+        <v>7.874199996876996e-06</v>
       </c>
     </row>
     <row r="5">
@@ -609,20 +609,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-21.42 (2.66)</t>
+          <t>-21.42</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1196343451738358</v>
+        <v>0.09624408748000861</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02563889697194099</v>
+        <v>0.02563889695331454</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3684929609298706</v>
+        <v>0.3376447867155075</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03090208023786545</v>
+        <v>0.03090207913704216</v>
       </c>
       <c r="H5" t="n">
         <v>0.9691185355186462</v>
@@ -634,7 +634,7 @@
         <v>0.3084602057933807</v>
       </c>
       <c r="K5" t="n">
-        <v>7.053499997709878e-06</v>
+        <v>5.883300000277813e-06</v>
       </c>
     </row>
     <row r="6">
@@ -650,20 +650,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-21.37 (2.62)</t>
+          <t>-21.37</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.117014154791832</v>
+        <v>0.09292872367799282</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02560588344931602</v>
+        <v>0.0256058842279017</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3813428282737732</v>
+        <v>0.3510798379182816</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03301497548818588</v>
+        <v>0.03301497193425894</v>
       </c>
       <c r="H6" t="n">
         <v>0.1357849091291428</v>
@@ -675,7 +675,7 @@
         <v>0.3026606142520905</v>
       </c>
       <c r="K6" t="n">
-        <v>6.890800003020559e-06</v>
+        <v>6.434800001443363e-06</v>
       </c>
     </row>
     <row r="7">
@@ -691,20 +691,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-21.90 (2.68)</t>
+          <t>-21.90</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>37.79097747802734</v>
+        <v>36.67832434463501</v>
       </c>
       <c r="E7" t="n">
-        <v>3.034065723419189</v>
+        <v>3.034065952301026</v>
       </c>
       <c r="F7" t="n">
-        <v>959.1118774414062</v>
+        <v>935.141348022461</v>
       </c>
       <c r="G7" t="n">
-        <v>8.012264251708984</v>
+        <v>8.012263132095336</v>
       </c>
       <c r="H7" t="n">
         <v>0.5832287073135376</v>
@@ -716,7 +716,7 @@
         <v>0.2876628041267395</v>
       </c>
       <c r="K7" t="n">
-        <v>5.949300000793301e-06</v>
+        <v>6.014400001731701e-06</v>
       </c>
     </row>
     <row r="8">
@@ -732,20 +732,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-21.73 (2.66)</t>
+          <t>-21.73</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>38.44820404052734</v>
+        <v>37.48207948684692</v>
       </c>
       <c r="E8" t="n">
-        <v>3.03003978729248</v>
+        <v>3.030039930820465</v>
       </c>
       <c r="F8" t="n">
-        <v>951.8540649414062</v>
+        <v>929.5084318237305</v>
       </c>
       <c r="G8" t="n">
-        <v>8.152113914489746</v>
+        <v>8.152114129543305</v>
       </c>
       <c r="H8" t="n">
         <v>0.5626966953277588</v>
@@ -757,7 +757,7 @@
         <v>0.281400203704834</v>
       </c>
       <c r="K8" t="n">
-        <v>6.471200002124533e-06</v>
+        <v>6.240100003196858e-06</v>
       </c>
     </row>
     <row r="9">
@@ -773,20 +773,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-21.75 (2.67)</t>
+          <t>-21.75</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>38.1599235534668</v>
+        <v>37.27782392120361</v>
       </c>
       <c r="E9" t="n">
-        <v>3.020694732666016</v>
+        <v>3.020694761514664</v>
       </c>
       <c r="F9" t="n">
-        <v>953.0140991210938</v>
+        <v>927.156200378418</v>
       </c>
       <c r="G9" t="n">
-        <v>8.096363067626953</v>
+        <v>8.09636275100708</v>
       </c>
       <c r="H9" t="n">
         <v>0.5651940703392029</v>
@@ -798,7 +798,7 @@
         <v>0.2835347056388855</v>
       </c>
       <c r="K9" t="n">
-        <v>7.677699999476318e-06</v>
+        <v>6.375999997544568e-06</v>
       </c>
     </row>
     <row r="10">
@@ -814,20 +814,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-22.31 (2.63)</t>
+          <t>-22.31</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>38.21701431274414</v>
+        <v>37.2257766456604</v>
       </c>
       <c r="E10" t="n">
-        <v>3.010962247848511</v>
+        <v>3.01096231508255</v>
       </c>
       <c r="F10" t="n">
-        <v>955.25537109375</v>
+        <v>930.6664410400391</v>
       </c>
       <c r="G10" t="n">
-        <v>8.081099510192871</v>
+        <v>8.081100230693817</v>
       </c>
       <c r="H10" t="n">
         <v>0.5666752457618713</v>
@@ -839,7 +839,7 @@
         <v>0.2849827110767365</v>
       </c>
       <c r="K10" t="n">
-        <v>6.067599999369122e-06</v>
+        <v>6.2783000030322e-06</v>
       </c>
     </row>
     <row r="11">
@@ -855,20 +855,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-21.96 (2.66)</t>
+          <t>-21.96</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>38.16988372802734</v>
+        <v>37.20124872970581</v>
       </c>
       <c r="E11" t="n">
-        <v>3.017095327377319</v>
+        <v>3.01709536409378</v>
       </c>
       <c r="F11" t="n">
-        <v>945.5015258789062</v>
+        <v>922.7560665283203</v>
       </c>
       <c r="G11" t="n">
-        <v>8.08076000213623</v>
+        <v>8.080758974075318</v>
       </c>
       <c r="H11" t="n">
         <v>0.5625405311584473</v>
@@ -880,7 +880,7 @@
         <v>0.2848705351352692</v>
       </c>
       <c r="K11" t="n">
-        <v>6.383100000675768e-06</v>
+        <v>5.922399999690242e-06</v>
       </c>
     </row>
     <row r="12">
@@ -896,20 +896,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-23.75 (2.64)</t>
+          <t>-23.75</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>39.31764221191406</v>
+        <v>38.34482963180542</v>
       </c>
       <c r="E12" t="n">
-        <v>2.962957143783569</v>
+        <v>2.962956932783127</v>
       </c>
       <c r="F12" t="n">
-        <v>984.1077880859375</v>
+        <v>938.5292324829102</v>
       </c>
       <c r="G12" t="n">
-        <v>8.326436996459961</v>
+        <v>8.326436245918273</v>
       </c>
       <c r="H12" t="n">
         <v>0.5311014652252197</v>
@@ -921,7 +921,7 @@
         <v>0.3029690682888031</v>
       </c>
       <c r="K12" t="n">
-        <v>7.781699998304247e-06</v>
+        <v>6.455800001276657e-06</v>
       </c>
     </row>
     <row r="13">
@@ -937,20 +937,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-23.88 (2.66)</t>
+          <t>-23.88</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>39.23785400390625</v>
+        <v>38.32909970092773</v>
       </c>
       <c r="E13" t="n">
-        <v>2.96320104598999</v>
+        <v>2.963200966358185</v>
       </c>
       <c r="F13" t="n">
-        <v>980.4300537109375</v>
+        <v>942.3364686279297</v>
       </c>
       <c r="G13" t="n">
-        <v>8.356050491333008</v>
+        <v>8.356051283836365</v>
       </c>
       <c r="H13" t="n">
         <v>0.5334012508392334</v>
@@ -962,7 +962,7 @@
         <v>0.3073286116123199</v>
       </c>
       <c r="K13" t="n">
-        <v>6.074099997931626e-06</v>
+        <v>1.449239999783458e-05</v>
       </c>
     </row>
     <row r="14">
@@ -978,20 +978,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-23.80 (2.65)</t>
+          <t>-23.80</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>39.48330307006836</v>
+        <v>38.50835977554321</v>
       </c>
       <c r="E14" t="n">
-        <v>2.967262506484985</v>
+        <v>2.967262668132782</v>
       </c>
       <c r="F14" t="n">
-        <v>995.008544921875</v>
+        <v>949.3453792724609</v>
       </c>
       <c r="G14" t="n">
-        <v>8.401307106018066</v>
+        <v>8.401307012557984</v>
       </c>
       <c r="H14" t="n">
         <v>0.5297303795814514</v>
@@ -1003,7 +1003,7 @@
         <v>0.305938184261322</v>
       </c>
       <c r="K14" t="n">
-        <v>6.256499997107312e-06</v>
+        <v>5.985100004181732e-06</v>
       </c>
     </row>
     <row r="15">
@@ -1019,20 +1019,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-23.85 (2.66)</t>
+          <t>-23.85</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>39.12985992431641</v>
+        <v>38.15680184936524</v>
       </c>
       <c r="E15" t="n">
-        <v>2.958388090133667</v>
+        <v>2.958388218402863</v>
       </c>
       <c r="F15" t="n">
-        <v>980.7908325195312</v>
+        <v>932.182260131836</v>
       </c>
       <c r="G15" t="n">
-        <v>8.282486915588379</v>
+        <v>8.282486514091492</v>
       </c>
       <c r="H15" t="n">
         <v>0.5341669917106628</v>
@@ -1044,7 +1044,7 @@
         <v>0.3058680295944214</v>
       </c>
       <c r="K15" t="n">
-        <v>6.426600004488137e-06</v>
+        <v>6.488500002888031e-06</v>
       </c>
     </row>
     <row r="16">
@@ -1060,20 +1060,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-23.61 (2.66)</t>
+          <t>-23.61</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>39.22180938720703</v>
+        <v>38.29413411712647</v>
       </c>
       <c r="E16" t="n">
-        <v>2.961922645568848</v>
+        <v>2.961922732591629</v>
       </c>
       <c r="F16" t="n">
-        <v>980.8865966796875</v>
+        <v>939.2883869628906</v>
       </c>
       <c r="G16" t="n">
-        <v>8.327680587768555</v>
+        <v>8.327680652618408</v>
       </c>
       <c r="H16" t="n">
         <v>0.5311251282691956</v>
@@ -1085,7 +1085,7 @@
         <v>0.3027482926845551</v>
       </c>
       <c r="K16" t="n">
-        <v>6.700300000375137e-06</v>
+        <v>6.46229999983916e-06</v>
       </c>
     </row>
     <row r="17">
@@ -1101,20 +1101,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-18.52 (2.72)</t>
+          <t>-18.52</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.07514205574989319</v>
+        <v>0.06072998848930002</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02299807965755463</v>
+        <v>0.0229980776719749</v>
       </c>
       <c r="F17" t="n">
-        <v>0.005046725273132324</v>
+        <v>0.003742030739784241</v>
       </c>
       <c r="G17" t="n">
-        <v>1.595467801962513e-05</v>
+        <v>1.595467791321426e-05</v>
       </c>
       <c r="H17" t="n">
         <v>0.0548088327050209</v>
@@ -1126,7 +1126,7 @@
         <v>0.3149725496768951</v>
       </c>
       <c r="K17" t="n">
-        <v>9.185999995679595e-06</v>
+        <v>9.06159999431111e-06</v>
       </c>
     </row>
     <row r="18">
@@ -1142,20 +1142,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-18.24 (2.73)</t>
+          <t>-18.24</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.07990183681249619</v>
+        <v>0.06529260030388832</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02297288365662098</v>
+        <v>0.02297288282960653</v>
       </c>
       <c r="F18" t="n">
-        <v>0.005101442337036133</v>
+        <v>0.003535274505615234</v>
       </c>
       <c r="G18" t="n">
-        <v>1.50457417475991e-05</v>
+        <v>1.504573960301059e-05</v>
       </c>
       <c r="H18" t="n">
         <v>0.05438490584492683</v>
@@ -1167,7 +1167,7 @@
         <v>0.3141289055347443</v>
       </c>
       <c r="K18" t="n">
-        <v>8.90600000275299e-06</v>
+        <v>9.01470000098925e-06</v>
       </c>
     </row>
     <row r="19">
@@ -1183,20 +1183,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-18.57 (2.68)</t>
+          <t>-18.57</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.07461848855018616</v>
+        <v>0.06389518796652556</v>
       </c>
       <c r="E19" t="n">
-        <v>0.02308282814919949</v>
+        <v>0.02308282779343426</v>
       </c>
       <c r="F19" t="n">
-        <v>0.004960298538208008</v>
+        <v>0.003997717022895813</v>
       </c>
       <c r="G19" t="n">
-        <v>1.653458093642257e-05</v>
+        <v>1.653458106102334e-05</v>
       </c>
       <c r="H19" t="n">
         <v>0.05574209243059158</v>
@@ -1208,7 +1208,7 @@
         <v>0.3117594718933105</v>
       </c>
       <c r="K19" t="n">
-        <v>8.867500000633299e-06</v>
+        <v>8.710300004167948e-06</v>
       </c>
     </row>
     <row r="20">
@@ -1224,20 +1224,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-18.42 (2.69)</t>
+          <t>-18.42</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.07324337214231491</v>
+        <v>0.06355301559343934</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0232883132994175</v>
+        <v>0.02328831494040787</v>
       </c>
       <c r="F20" t="n">
-        <v>0.004958510398864746</v>
+        <v>0.003874084949493408</v>
       </c>
       <c r="G20" t="n">
-        <v>1.652943319641054e-05</v>
+        <v>1.652943236513238e-05</v>
       </c>
       <c r="H20" t="n">
         <v>0.0551995262503624</v>
@@ -1249,7 +1249,7 @@
         <v>0.3145458400249481</v>
       </c>
       <c r="K20" t="n">
-        <v>9.264899999834597e-06</v>
+        <v>9.167099997284821e-06</v>
       </c>
     </row>
     <row r="21">
@@ -1265,20 +1265,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-18.50 (2.67)</t>
+          <t>-18.50</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.07633413374423981</v>
+        <v>0.06380707132443786</v>
       </c>
       <c r="E21" t="n">
-        <v>0.02324997074902058</v>
+        <v>0.02324996946938336</v>
       </c>
       <c r="F21" t="n">
-        <v>0.005114316940307617</v>
+        <v>0.003707248449325561</v>
       </c>
       <c r="G21" t="n">
-        <v>1.581008837092668e-05</v>
+        <v>1.581008816719987e-05</v>
       </c>
       <c r="H21" t="n">
         <v>0.05478144809603691</v>
@@ -1290,7 +1290,7 @@
         <v>0.3127709329128265</v>
       </c>
       <c r="K21" t="n">
-        <v>8.950600000389386e-06</v>
+        <v>8.963899999798741e-06</v>
       </c>
     </row>
     <row r="22">
@@ -1306,20 +1306,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>8.54 (2.31)</t>
+          <t>8.54</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.25540292263031</v>
+        <v>1.069020014822483</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1131935641169548</v>
+        <v>0.1131935617104173</v>
       </c>
       <c r="F22" t="n">
-        <v>0.003107786178588867</v>
+        <v>0.002146059036254883</v>
       </c>
       <c r="G22" t="n">
-        <v>4.645149601856247e-06</v>
+        <v>4.645149432690232e-06</v>
       </c>
       <c r="H22" t="n">
         <v>0.04186482727527618</v>
@@ -1331,7 +1331,7 @@
         <v>0.2798687517642975</v>
       </c>
       <c r="K22" t="n">
-        <v>9.724899995489977e-06</v>
+        <v>8.606600000348408e-06</v>
       </c>
     </row>
     <row r="23">
@@ -1347,20 +1347,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>9.40 (2.33)</t>
+          <t>9.40</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1.022862672805786</v>
+        <v>0.9600494065880776</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1552429050207138</v>
+        <v>0.1552429073750973</v>
       </c>
       <c r="F23" t="n">
-        <v>0.007849574089050293</v>
+        <v>0.006255125045776367</v>
       </c>
       <c r="G23" t="n">
-        <v>3.04658169625327e-05</v>
+        <v>3.046581961825723e-05</v>
       </c>
       <c r="H23" t="n">
         <v>0.05201252922415733</v>
@@ -1372,7 +1372,7 @@
         <v>0.294763058423996</v>
       </c>
       <c r="K23" t="n">
-        <v>1.957930000207852e-05</v>
+        <v>9.081600001081825e-06</v>
       </c>
     </row>
     <row r="24">
@@ -1388,20 +1388,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>7.42 (2.28)</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1.149510741233826</v>
+        <v>0.9546271737813949</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1058946177363396</v>
+        <v>0.1058946109116077</v>
       </c>
       <c r="F24" t="n">
-        <v>0.01351070404052734</v>
+        <v>0.01004328989982605</v>
       </c>
       <c r="G24" t="n">
-        <v>3.617384209064767e-05</v>
+        <v>3.617384266181034e-05</v>
       </c>
       <c r="H24" t="n">
         <v>0.05830847471952438</v>
@@ -1413,7 +1413,7 @@
         <v>0.302911102771759</v>
       </c>
       <c r="K24" t="n">
-        <v>8.988399997178932e-06</v>
+        <v>8.570400001190137e-06</v>
       </c>
     </row>
     <row r="25">
@@ -1429,20 +1429,20 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>12.54 (2.40)</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.8676587343215942</v>
+        <v>0.7812392020821571</v>
       </c>
       <c r="E25" t="n">
-        <v>0.09677117317914963</v>
+        <v>0.09677117650210858</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02125382423400879</v>
+        <v>0.01393528139591217</v>
       </c>
       <c r="G25" t="n">
-        <v>6.544401549035683e-05</v>
+        <v>6.544401349674444e-05</v>
       </c>
       <c r="H25" t="n">
         <v>0.06584927439689636</v>
@@ -1454,7 +1454,7 @@
         <v>0.2694041430950165</v>
       </c>
       <c r="K25" t="n">
-        <v>8.920000000216533e-06</v>
+        <v>9.037299998453818e-06</v>
       </c>
     </row>
     <row r="26">
@@ -1470,14 +1470,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>8.96 (2.32)</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.8835476040840149</v>
+        <v>0.829081823527813</v>
       </c>
       <c r="E26" t="n">
-        <v>0.09112653881311417</v>
+        <v>0.09112653527408839</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0.2688374519348145</v>
       </c>
       <c r="K26" t="n">
-        <v>1.131120000354713e-05</v>
+        <v>9.546000001137145e-06</v>
       </c>
     </row>
     <row r="27">
@@ -1511,20 +1511,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-330.00 (5.07)</t>
+          <t>-330.00</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.1662453711032867</v>
+        <v>0.1566219767332077</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02684792131185532</v>
+        <v>0.02684792033210397</v>
       </c>
       <c r="F27" t="n">
-        <v>17.7396240234375</v>
+        <v>17.60419565582275</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3625338971614838</v>
+        <v>0.362533863991499</v>
       </c>
       <c r="H27" t="n">
         <v>1.101846694946289</v>
@@ -1536,7 +1536,7 @@
         <v>1.37524151802063</v>
       </c>
       <c r="K27" t="n">
-        <v>5.481599997438025e-06</v>
+        <v>6.744500002241693e-06</v>
       </c>
     </row>
     <row r="28">
@@ -1552,20 +1552,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-328.60 (5.01)</t>
+          <t>-328.60</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.1961507499217987</v>
+        <v>0.1763519300222397</v>
       </c>
       <c r="E28" t="n">
-        <v>0.02809842675924301</v>
+        <v>0.028098428029567</v>
       </c>
       <c r="F28" t="n">
-        <v>17.73380661010742</v>
+        <v>17.55601633644104</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3579410910606384</v>
+        <v>0.3579410746395588</v>
       </c>
       <c r="H28" t="n">
         <v>1.094076871871948</v>
@@ -1577,7 +1577,7 @@
         <v>1.378463745117188</v>
       </c>
       <c r="K28" t="n">
-        <v>5.754600002546795e-06</v>
+        <v>5.999799999699462e-06</v>
       </c>
     </row>
     <row r="29">
@@ -1593,20 +1593,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-331.84 (5.18)</t>
+          <t>-331.84</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.1567540913820267</v>
+        <v>0.1424202823936939</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0263974517583847</v>
+        <v>0.02639745533652604</v>
       </c>
       <c r="F29" t="n">
-        <v>17.76790618896484</v>
+        <v>17.65824348449707</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3668395578861237</v>
+        <v>0.3668395908474922</v>
       </c>
       <c r="H29" t="n">
         <v>0.109405018389225</v>
@@ -1618,7 +1618,7 @@
         <v>1.375186085700989</v>
       </c>
       <c r="K29" t="n">
-        <v>5.73150000127498e-06</v>
+        <v>6.664499996986706e-06</v>
       </c>
     </row>
     <row r="30">
@@ -1634,20 +1634,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-327.93 (5.07)</t>
+          <t>-327.93</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.2222423553466797</v>
+        <v>0.1455211078673601</v>
       </c>
       <c r="E30" t="n">
-        <v>0.02826853841543198</v>
+        <v>0.02826853665336966</v>
       </c>
       <c r="F30" t="n">
-        <v>17.66987228393555</v>
+        <v>17.50471514892578</v>
       </c>
       <c r="G30" t="n">
-        <v>0.3547891080379486</v>
+        <v>0.3547890853285789</v>
       </c>
       <c r="H30" t="n">
         <v>1.09808075428009</v>
@@ -1659,7 +1659,7 @@
         <v>1.369550943374634</v>
       </c>
       <c r="K30" t="n">
-        <v>5.701099995349068e-06</v>
+        <v>6.521900002553594e-06</v>
       </c>
     </row>
     <row r="31">
@@ -1675,20 +1675,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-284.20 (4.19)</t>
+          <t>-284.20</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.1142737120389938</v>
+        <v>0.08124188476800918</v>
       </c>
       <c r="E31" t="n">
-        <v>0.02001002244651318</v>
+        <v>0.02001002448424697</v>
       </c>
       <c r="F31" t="n">
-        <v>16.6176586151123</v>
+        <v>16.4855033416748</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3871499001979828</v>
+        <v>0.3871498747169971</v>
       </c>
       <c r="H31" t="n">
         <v>0.9303419589996338</v>
@@ -1700,7 +1700,7 @@
         <v>2.835822105407715</v>
       </c>
       <c r="K31" t="n">
-        <v>6.78679999691667e-06</v>
+        <v>6.189599997014738e-06</v>
       </c>
     </row>
   </sheetData>
